--- a/output/pdf_financials_xlsx/MD.xlsx
+++ b/output/pdf_financials_xlsx/MD.xlsx
@@ -1035,46 +1035,46 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.069912</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.054311</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.066743</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.056565</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.121237</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.225491</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.169368</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.203475</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.330999</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.09883699999999999</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.080524</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.251035</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.311674</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.233882</v>
       </c>
     </row>
     <row r="13">
@@ -1932,46 +1932,46 @@
         <v>-1.014932</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.9859520000000001</v>
+        <v>-1.055864</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.42069</v>
+        <v>-1.475001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.130443</v>
+        <v>-1.197186</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.130449</v>
+        <v>-2.187014</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.868395</v>
+        <v>-0.989632</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.999292</v>
+        <v>-1.224783</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.596146</v>
+        <v>-1.765514</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.5016</v>
+        <v>-1.705075</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.584212</v>
+        <v>-2.915211</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.626974</v>
+        <v>-1.725811</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.75644</v>
+        <v>-2.836964</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.249259</v>
+        <v>-2.500294</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.979998</v>
+        <v>-3.291672</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.552956</v>
+        <v>-2.786838</v>
       </c>
     </row>
     <row r="28">
@@ -2042,46 +2042,46 @@
         <v>-1.014932</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.9859520000000001</v>
+        <v>-1.055864</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.42069</v>
+        <v>-1.475001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.130443</v>
+        <v>-1.197186</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.130449</v>
+        <v>-2.187014</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.868395</v>
+        <v>-0.989632</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.999292</v>
+        <v>-1.224783</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.596146</v>
+        <v>-1.765514</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.5016</v>
+        <v>-1.705075</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.584212</v>
+        <v>-2.915211</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.597082</v>
+        <v>-1.695919</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.726548</v>
+        <v>-2.807072</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.219367</v>
+        <v>-2.470402</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.950106</v>
+        <v>-3.26178</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.523282</v>
+        <v>-2.757164</v>
       </c>
     </row>
     <row r="30">
@@ -2107,16 +2107,16 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-5990.688924218336</v>
+        <v>-6344.387917329093</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-1234.448931818313</v>
+        <v>-1267.224465909157</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-288.0707376298714</v>
+        <v>-328.2884173931505</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-930.2402651201327</v>
+        <v>-1140.14968861417</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -2333,10 +2333,10 @@
         <v>2.752286</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.349389</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.49086</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.895705</v>
@@ -2443,10 +2443,10 @@
         <v>2.752286</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.349389</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.49086</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.895705</v>
@@ -3103,10 +3103,10 @@
         <v>7.46903</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>14.463479</v>
+        <v>14.11409</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.811522999999999</v>
+        <v>7.320663</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>4.765739</v>
@@ -10984,7 +10984,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -23988,7 +23988,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">

--- a/output/pdf_financials_xlsx/MD.xlsx
+++ b/output/pdf_financials_xlsx/MD.xlsx
@@ -750,37 +750,37 @@
         <v>0.18936</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.426494</v>
+        <v>0.473337</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.291498</v>
+        <v>0.36243</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.101138</v>
+        <v>0.181521</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.251113</v>
+        <v>0.338706</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.406134</v>
+        <v>0.498359</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.218734</v>
+        <v>0.30259</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.203688</v>
+        <v>0.337606</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.219908</v>
+        <v>0.371503</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.132178</v>
+        <v>0.305516</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.252363</v>
+        <v>0.448381</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.257403</v>
+        <v>0.447624</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0.358664</v>
@@ -4354,13 +4354,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.034496</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.016612</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.022392</v>
       </c>
     </row>
     <row r="71">
@@ -4409,13 +4409,13 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.034496</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.016612</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.022392</v>
       </c>
     </row>
     <row r="72">
@@ -4629,13 +4629,13 @@
         <v>0.578916</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.7544920000000001</v>
+        <v>0.719996</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>1.106105</v>
+        <v>1.089493</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.294994</v>
+        <v>1.272602</v>
       </c>
     </row>
     <row r="76">
@@ -4944,17 +4944,13 @@
         <v>0.001334616349112949</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.0004175856130947126</v>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001284731851314987</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.0004203229219659312</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.0005028554315112452</v>
       </c>
     </row>
     <row r="81">
@@ -9786,7 +9782,11 @@
           <t>Lease liabilities (note 6)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10602,7 +10602,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -14612,7 +14616,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -14692,7 +14700,11 @@
           <t>Flow-through private placement</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -18264,7 +18276,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -19186,7 +19202,11 @@
           <t>Future income taxes recovery</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>-0.112</v>
       </c>
@@ -22584,7 +22604,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
